--- a/Datasets/vjcortesa_Risk_Perceptiondataset_240924.xlsx
+++ b/Datasets/vjcortesa_Risk_Perceptiondataset_240924.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W79"/>
+  <dimension ref="A1:Y79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="20.7109375" style="2" customWidth="1"/>
@@ -477,6 +477,16 @@
           <t>Q_Threatcode</t>
         </is>
       </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Q_Responsibility</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Q_Responsibilitycode</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -590,6 +600,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Public authorities are completely responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -703,6 +723,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -816,6 +846,16 @@
           <t>4</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Public authorities are completely responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -929,6 +969,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -1042,6 +1092,16 @@
           <t>2</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -1155,6 +1215,16 @@
           <t>4</t>
         </is>
       </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -1268,6 +1338,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Public authorities are completely responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -1381,6 +1461,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Public authorities are completely responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -1494,6 +1584,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -1607,6 +1707,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Public authorities are completely responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -1720,6 +1830,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -1833,6 +1953,16 @@
           <t>2</t>
         </is>
       </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -1946,6 +2076,16 @@
           <t>4</t>
         </is>
       </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Public authorities are completely responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -2059,6 +2199,16 @@
           <t>4</t>
         </is>
       </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -2172,6 +2322,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -2285,6 +2445,16 @@
           <t>4</t>
         </is>
       </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -2398,6 +2568,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -2511,6 +2691,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -2624,6 +2814,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -2737,6 +2937,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Public authorities are completely responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -2850,6 +3060,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Public authorities are completely responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -2963,6 +3183,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -3076,6 +3306,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -3189,6 +3429,16 @@
           <t>4</t>
         </is>
       </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -3302,6 +3552,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -3415,6 +3675,16 @@
           <t>2</t>
         </is>
       </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Public authorities are completely responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -3528,6 +3798,16 @@
           <t>2</t>
         </is>
       </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -3641,6 +3921,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Public authorities are completely responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -3754,6 +4044,16 @@
           <t>4</t>
         </is>
       </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -3867,6 +4167,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Public authorities are completely responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -3980,6 +4290,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Public authorities are completely responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -4093,6 +4413,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -4206,6 +4536,16 @@
           <t>2</t>
         </is>
       </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Public authorities are completely responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -4319,6 +4659,16 @@
           <t>2</t>
         </is>
       </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -4432,6 +4782,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -4545,6 +4905,16 @@
           <t>4</t>
         </is>
       </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Public authorities are completely responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -4658,6 +5028,16 @@
           <t>2</t>
         </is>
       </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -4771,6 +5151,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Public authorities are completely responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -4884,6 +5274,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -4997,6 +5397,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -5110,6 +5520,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Public authorities are completely responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -5223,6 +5643,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -5336,6 +5766,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -5449,6 +5889,16 @@
           <t>5</t>
         </is>
       </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -5562,6 +6012,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Public authorities are completely responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -5675,6 +6135,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -5788,6 +6258,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Public authorities are completely responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -5901,6 +6381,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -6014,6 +6504,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -6127,6 +6627,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Public authorities are completely responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -6240,6 +6750,16 @@
           <t>4</t>
         </is>
       </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Public authorities and citizens are equally responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -6353,6 +6873,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Public authorities and citizens are equally responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -6466,6 +6996,16 @@
           <t>2</t>
         </is>
       </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Public authorities are completely responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -6579,6 +7119,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -6692,6 +7242,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -6805,6 +7365,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -6918,6 +7488,16 @@
           <t>4</t>
         </is>
       </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Public authorities are completely responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -7031,6 +7611,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -7144,6 +7734,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Public authorities are completely responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -7257,6 +7857,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Public authorities are completely responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -7370,6 +7980,16 @@
           <t>4</t>
         </is>
       </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -7483,6 +8103,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -7596,6 +8226,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Public authorities and citizens are equally responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65">
@@ -7709,6 +8349,16 @@
           <t>2</t>
         </is>
       </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Public authorities are completely responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66">
@@ -7822,6 +8472,16 @@
           <t>5</t>
         </is>
       </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Public authorities are completely responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67">
@@ -7935,6 +8595,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Public authorities are completely responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68">
@@ -8048,6 +8718,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69">
@@ -8161,6 +8841,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70">
@@ -8274,6 +8964,16 @@
           <t>4</t>
         </is>
       </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71">
@@ -8387,6 +9087,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72">
@@ -8500,6 +9210,16 @@
           <t>2</t>
         </is>
       </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Public authorities are completely responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73">
@@ -8613,6 +9333,16 @@
           <t>4</t>
         </is>
       </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Public authorities and citizens are equally responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74">
@@ -8726,6 +9456,16 @@
           <t>2</t>
         </is>
       </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75">
@@ -8839,6 +9579,16 @@
           <t>4</t>
         </is>
       </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Public authorities are completely responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76">
@@ -8952,6 +9702,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77">
@@ -9065,6 +9825,16 @@
           <t>4</t>
         </is>
       </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78">
@@ -9178,6 +9948,16 @@
           <t>4</t>
         </is>
       </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79">
@@ -9289,6 +10069,16 @@
       <c r="W79" t="inlineStr">
         <is>
           <t>4</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Public authorities are responsible and citizens somewhat responsible for flood protection</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
